--- a/output/pdf_financials_xlsx/DSY.xlsx
+++ b/output/pdf_financials_xlsx/DSY.xlsx
@@ -827,22 +827,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.021132</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.014314</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.010597</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.027188</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.024415</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.004031</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1438,22 +1438,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.376502</v>
+        <v>-0.397634</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.577562</v>
+        <v>0.563248</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.31254</v>
+        <v>1.301943</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.221556</v>
+        <v>1.194368</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.33883</v>
+        <v>0.314415</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.382529</v>
+        <v>0.378498</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.153422</v>
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.185119</v>
+        <v>-0.206251</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.730947</v>
+        <v>0.716633</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.418409</v>
+        <v>1.407812</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.318402</v>
+        <v>1.291214</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.474215</v>
+        <v>0.4498</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.487886</v>
+        <v>0.483855</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.296084</v>
@@ -1559,16 +1559,16 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>475.3253934210879</v>
+        <v>471.7742151684942</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>425.2470712700625</v>
+        <v>416.4776539195954</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>148.827961949955</v>
+        <v>141.1655415477995</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>123.8525099955575</v>
+        <v>122.8292187599162</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>45.0798493907573</v>
@@ -20738,7 +20738,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" s="5" t="n">

--- a/output/pdf_financials_xlsx/DSY.xlsx
+++ b/output/pdf_financials_xlsx/DSY.xlsx
@@ -4585,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.003734</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -14734,7 +14734,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DSY.xlsx
+++ b/output/pdf_financials_xlsx/DSY.xlsx
@@ -11154,7 +11154,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -15400,7 +15404,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E157" s="5" t="n">
         <v>-0.188251</v>
       </c>
